--- a/naver-place-crawler/results_health/평택_헬스장.xlsx
+++ b/naver-place-crawler/results_health/평택_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/planner_fitness2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q2" t="n">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="R2" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스테디휘트니스 평택점</t>
+          <t>아세로짐 용죽점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>steadyfitness06@naver.com</t>
+          <t>acero_yong@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1381-3717</t>
+          <t>0507-1412-0716</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 세교8길 30 7층</t>
+          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/stea_dy06</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6ejzs8</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1071</v>
+        <v>124</v>
       </c>
       <c r="Q3" t="n">
-        <v>527</v>
+        <v>222</v>
       </c>
       <c r="R3" t="n">
-        <v>1598</v>
+        <v>346</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,61 +738,61 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1573654594</t>
+          <t>1478339886</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573654594</t>
+          <t>https://m.place.naver.com/place/1478339886</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용 24시 헬스PT 그레이스짐</t>
+          <t>스테디휘트니스 평택점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>minho8802@naver.com</t>
+          <t>steadyfitness06@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-653-0788</t>
+          <t>0507-1381-3717</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기 평택시 세교8길 30 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kQTJd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,32 +802,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1240</v>
+        <v>1082</v>
       </c>
       <c r="Q4" t="n">
-        <v>1196</v>
+        <v>527</v>
       </c>
       <c r="R4" t="n">
-        <v>2436</v>
+        <v>1609</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38320515</t>
+          <t>1573654594</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38320515</t>
+          <t>https://m.place.naver.com/place/1573654594</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2 피트니스</t>
+          <t>24시 라이트짐 고덕2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h2fit@naver.com</t>
+          <t>lightgym12@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1422-4242</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 서정북로 79 신광빌딩 4층</t>
+          <t>경기 평택시 고덕중앙로 200-20 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h2fit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +882,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh8wgd8</t>
+          <t>https://talk.naver.com/ct/w6vxgc6</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>231</v>
+        <v>1720</v>
       </c>
       <c r="Q5" t="n">
-        <v>353</v>
+        <v>820</v>
       </c>
       <c r="R5" t="n">
-        <v>584</v>
+        <v>2540</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38427855</t>
+          <t>1517230352</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38427855</t>
+          <t>https://m.place.naver.com/place/1517230352</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,25 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 라이트짐 고덕2호점</t>
+          <t>원페이스짐 헬스&amp;PT 평택용죽점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lightgym12@naver.com</t>
+          <t>oneface11@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1361-1061</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 고덕중앙로 200-20 9층</t>
+          <t>경기 평택시 소사5길 120 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym12/223986584742</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w6vxgc6</t>
+          <t>https://talk.naver.com/ct/wxvlog7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1688</v>
+        <v>638</v>
       </c>
       <c r="Q6" t="n">
-        <v>818</v>
+        <v>362</v>
       </c>
       <c r="R6" t="n">
-        <v>2506</v>
+        <v>1000</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1517230352</t>
+          <t>1772871167</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517230352</t>
+          <t>https://m.place.naver.com/place/1772871167</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jaygym/category/ALL?cp=1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="Q7" t="n">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="R7" t="n">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,41 +1132,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>여성전용 24시 헬스PT 그레이스짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>minho8802@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>031-653-0788</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,27 +1191,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa9rmy3</t>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2850</v>
+        <v>1244</v>
       </c>
       <c r="Q8" t="n">
-        <v>1240</v>
+        <v>1061</v>
       </c>
       <c r="R8" t="n">
-        <v>4090</v>
+        <v>2305</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>38320515</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/38320515</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스포데이 휘트니스 평택 용이점</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spoday5pt-health@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1337-2949</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 서동대로 3879 제이플러스빌딩 3층</t>
+          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoday5pt-health</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4i9su</t>
+          <t>https://talk.naver.com/ct/wa9rmy3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>901</v>
+        <v>2878</v>
       </c>
       <c r="Q9" t="n">
-        <v>793</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>1694</v>
+        <v>4124</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1594380254</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594380254</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1340,93 +1340,285 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>어라이브 피트니스</t>
+          <t>스포데이 휘트니스 평택 용이점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shdrml@naver.com</t>
+          <t>spoday5pt-health@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-647-3512</t>
+          <t>0507-1337-2949</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>경기 평택시 서동대로 3879 제이플러스빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoday5pt-health</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4i9su</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>911</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>798</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1709</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1594380254</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594380254</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>어라이브 피트니스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>alivefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>031-647-3512</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>경기 평택시 만세로 1770-3 1동 3층 302호</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/shdrml</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5u2sq</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>122</v>
       </c>
-      <c r="Q10" t="n">
-        <v>468</v>
-      </c>
-      <c r="R10" t="n">
-        <v>590</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>473</v>
+      </c>
+      <c r="R11" t="n">
+        <v>595</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1389618749</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1389618749</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>365일 24시 라이트짐 평택역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lightgym3871@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 평택시 평택로32번길 34 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lightgym3871/224146200506</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1648</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>819</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2467</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1099573478</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099573478</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/평택_헬스장.xlsx
+++ b/naver-place-crawler/results_health/평택_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>171</v>
       </c>
       <c r="Q2" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="R2" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -820,10 +820,10 @@
         <v>1082</v>
       </c>
       <c r="Q4" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R4" t="n">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="Q5" t="n">
         <v>820</v>
       </c>
       <c r="R5" t="n">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -948,24 +948,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>원페이스짐 헬스&amp;PT 평택용죽점</t>
+          <t>보라짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oneface11@naver.com</t>
+          <t>alfo3514@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1361-1061</t>
+          <t>0507-1347-3825</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 소사5길 120 401호</t>
+          <t>경기 평택시 관광특구로 37 5층 보라짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxvlog7</t>
+          <t>https://talk.naver.com/ct/w4hjqv</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>638</v>
+        <v>316</v>
       </c>
       <c r="Q6" t="n">
-        <v>362</v>
+        <v>466</v>
       </c>
       <c r="R6" t="n">
-        <v>1000</v>
+        <v>782</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1772871167</t>
+          <t>1406732485</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772871167</t>
+          <t>https://m.place.naver.com/place/1406732485</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1046,24 +1046,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>보라짐</t>
+          <t>H2 피트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>alfo3514@naver.com</t>
+          <t>h2fit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1347-3825</t>
+          <t>0507-1422-4242</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 관광특구로 37 5층 보라짐</t>
+          <t>경기 평택시 서정북로 79 신광빌딩 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hjqv</t>
+          <t>https://talk.naver.com/ct/wh8wgd8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="Q7" t="n">
-        <v>460</v>
+        <v>347</v>
       </c>
       <c r="R7" t="n">
-        <v>776</v>
+        <v>579</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1406732485</t>
+          <t>38427855</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406732485</t>
+          <t>https://m.place.naver.com/place/38427855</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1208,10 +1208,10 @@
         <v>1244</v>
       </c>
       <c r="Q8" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R8" t="n">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2878</v>
+        <v>2883</v>
       </c>
       <c r="Q9" t="n">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="R9" t="n">
-        <v>4124</v>
+        <v>4131</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoday5pt-health</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="Q10" t="n">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="R10" t="n">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym3871/224146200506</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="Q12" t="n">
         <v>819</v>
       </c>
       <c r="R12" t="n">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/평택_헬스장.xlsx
+++ b/naver-place-crawler/results_health/평택_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
+          <t>아세로짐 용죽점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>planner-22@naver.com</t>
+          <t>acero_yong@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-656-6637</t>
+          <t>0507-1412-0716</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 709 삼육빌딩 4층</t>
+          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/acero_yong</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ir3m</t>
+          <t>https://talk.naver.com/ct/w6ejzs8</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="Q2" t="n">
-        <v>488</v>
+        <v>222</v>
       </c>
       <c r="R2" t="n">
-        <v>659</v>
+        <v>346</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1816388747</t>
+          <t>1478339886</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816388747</t>
+          <t>https://m.place.naver.com/place/1478339886</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아세로짐 용죽점</t>
+          <t>스테디휘트니스 평택점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>acero_yong@naver.com</t>
+          <t>steadyfitness06@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1412-0716</t>
+          <t>0507-1381-3717</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
+          <t>경기 평택시 세교8길 30 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/stea_dy06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6ejzs8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>124</v>
+        <v>1082</v>
       </c>
       <c r="Q3" t="n">
-        <v>222</v>
+        <v>526</v>
       </c>
       <c r="R3" t="n">
-        <v>346</v>
+        <v>1608</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1478339886</t>
+          <t>1573654594</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478339886</t>
+          <t>https://m.place.naver.com/place/1573654594</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스테디휘트니스 평택점</t>
+          <t>24시 라이트짐 고덕2호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>steadyfitness06@naver.com</t>
+          <t>lightgym12@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1381-3717</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 세교8길 30 7층</t>
+          <t>경기 평택시 고덕중앙로 200-20 9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lightgym12/223986584742</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,20 +784,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6vxgc6</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1082</v>
+        <v>1722</v>
       </c>
       <c r="Q4" t="n">
-        <v>526</v>
+        <v>820</v>
       </c>
       <c r="R4" t="n">
-        <v>1608</v>
+        <v>2542</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1573654594</t>
+          <t>1517230352</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573654594</t>
+          <t>https://m.place.naver.com/place/1517230352</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,25 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 라이트짐 고덕2호점</t>
+          <t>보라짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lightgym12@naver.com</t>
+          <t>alfo3514@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1347-3825</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 고덕중앙로 200-20 9층</t>
+          <t>경기 평택시 관광특구로 37 5층 보라짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/jaygym/category/ALL?cp=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w6vxgc6</t>
+          <t>https://talk.naver.com/ct/w4hjqv</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1722</v>
+        <v>316</v>
       </c>
       <c r="Q5" t="n">
-        <v>820</v>
+        <v>467</v>
       </c>
       <c r="R5" t="n">
-        <v>2542</v>
+        <v>783</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1517230352</t>
+          <t>1406732485</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517230352</t>
+          <t>https://m.place.naver.com/place/1406732485</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보라짐</t>
+          <t>H2 피트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alfo3514@naver.com</t>
+          <t>h2fit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1347-3825</t>
+          <t>0507-1422-4242</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 관광특구로 37 5층 보라짐</t>
+          <t>경기 평택시 서정북로 79 신광빌딩 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/h2fit</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hjqv</t>
+          <t>https://talk.naver.com/ct/wh8wgd8</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="Q6" t="n">
-        <v>466</v>
+        <v>347</v>
       </c>
       <c r="R6" t="n">
-        <v>782</v>
+        <v>579</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1406732485</t>
+          <t>38427855</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406732485</t>
+          <t>https://m.place.naver.com/place/38427855</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1041,44 +1041,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2 피트니스</t>
+          <t>여성전용 24시 헬스PT 그레이스짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h2fit@naver.com</t>
+          <t>minho8802@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1422-4242</t>
+          <t>031-653-0788</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 서정북로 79 신광빌딩 4층</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_kQTJd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1093,27 +1093,27 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh8wgd8</t>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>232</v>
+        <v>1244</v>
       </c>
       <c r="Q7" t="n">
-        <v>347</v>
+        <v>1060</v>
       </c>
       <c r="R7" t="n">
-        <v>579</v>
+        <v>2304</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38427855</t>
+          <t>38320515</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38427855</t>
+          <t>https://m.place.naver.com/place/38320515</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>여성전용 24시 헬스PT 그레이스짐</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>minho8802@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-653-0788</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
+          <t>https://talk.naver.com/ct/wa9rmy3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1244</v>
+        <v>2883</v>
       </c>
       <c r="Q8" t="n">
-        <v>1060</v>
+        <v>1249</v>
       </c>
       <c r="R8" t="n">
-        <v>2304</v>
+        <v>4132</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38320515</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38320515</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>스포데이 휘트니스 평택 용이점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>spoday5pt-health@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>0507-1337-2949</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 서동대로 3879 제이플러스빌딩 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoday5pt-health</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa9rmy3</t>
+          <t>https://talk.naver.com/ct/w4i9su</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2883</v>
+        <v>913</v>
       </c>
       <c r="Q9" t="n">
-        <v>1248</v>
+        <v>800</v>
       </c>
       <c r="R9" t="n">
-        <v>4131</v>
+        <v>1713</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>1594380254</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/1594380254</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,29 +1340,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포데이 휘트니스 평택 용이점</t>
+          <t>몸애반하다 평택점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>spoday5pt-health@naver.com</t>
+          <t>yezzz7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1337-2949</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 서동대로 3879 제이플러스빌딩 3층</t>
+          <t>경기 평택시 송탄로 147 호원빌딩 F층 몸애반하다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/yezzz7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1368,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,27 +1383,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4i9su</t>
+          <t>https://talk.naver.com/ct/w4ihxj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>913</v>
+        <v>236</v>
       </c>
       <c r="Q10" t="n">
-        <v>800</v>
+        <v>81</v>
       </c>
       <c r="R10" t="n">
-        <v>1713</v>
+        <v>317</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594380254</t>
+          <t>1215316486</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594380254</t>
+          <t>https://m.place.naver.com/place/1215316486</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1433,34 +1429,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>어라이브 피트니스</t>
+          <t>365일 24시 라이트짐 평택역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>alivefit@naver.com</t>
+          <t>lightgym3871@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>031-647-3512</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 평택시 만세로 1770-3 1동 3층 302호</t>
+          <t>경기 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lightgym3871/224146200506</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,12 +1462,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1477,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u2sq</t>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1487,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>122</v>
+        <v>1651</v>
       </c>
       <c r="Q11" t="n">
-        <v>473</v>
+        <v>819</v>
       </c>
       <c r="R11" t="n">
-        <v>595</v>
+        <v>2470</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,109 +1506,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1389618749</t>
+          <t>1099573478</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389618749</t>
+          <t>https://m.place.naver.com/place/1099573478</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>365일 24시 라이트짐 평택역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>lightgym3871@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 평택시 평택로32번길 34 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pf7a</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1651</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>819</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2470</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1099573478</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1099573478</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/평택_헬스장.xlsx
+++ b/naver-place-crawler/results_health/평택_헬스장.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/planner_fitness2/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/stea_dy06</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -722,10 +722,10 @@
         <v>1082</v>
       </c>
       <c r="Q3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="R3" t="n">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym12/223986584742</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="Q4" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="R4" t="n">
-        <v>2547</v>
+        <v>2552</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jaygym/category/ALL?cp=1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q5" t="n">
         <v>468</v>
       </c>
       <c r="R5" t="n">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclemakergym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kQTJd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="Q7" t="n">
         <v>1060</v>
       </c>
       <c r="R7" t="n">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Q8" t="n">
         <v>1249</v>
       </c>
       <c r="R8" t="n">
-        <v>4135</v>
+        <v>4136</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1242,24 +1242,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스포데이 휘트니스 평택 용이점</t>
+          <t>어라이브 피트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spoday5pt-health@naver.com</t>
+          <t>alivefit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1337-2949</t>
+          <t>031-647-3512</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 서동대로 3879 제이플러스빌딩 3층</t>
+          <t>경기 평택시 만세로 1770-3 1동 3층 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4i9su</t>
+          <t>https://talk.naver.com/ct/w5u2sq</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>913</v>
+        <v>122</v>
       </c>
       <c r="Q9" t="n">
-        <v>800</v>
+        <v>474</v>
       </c>
       <c r="R9" t="n">
-        <v>1713</v>
+        <v>596</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1594380254</t>
+          <t>1389618749</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594380254</t>
+          <t>https://m.place.naver.com/place/1389618749</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1340,24 +1340,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>어라이브 피트니스</t>
+          <t>몸애반하다 평택점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>alivefit@naver.com</t>
+          <t>yezzz7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>031-647-3512</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 만세로 1770-3 1동 3층 302호</t>
+          <t>경기 평택시 송탄로 147 호원빌딩 F층 몸애반하다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1387,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u2sq</t>
+          <t>https://talk.naver.com/ct/w4ihxj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>122</v>
+        <v>236</v>
       </c>
       <c r="Q10" t="n">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="R10" t="n">
-        <v>596</v>
+        <v>317</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1389618749</t>
+          <t>1215316486</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389618749</t>
+          <t>https://m.place.naver.com/place/1215316486</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1452,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym3871/224146200506</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,12 +1462,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1495,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="Q11" t="n">
         <v>819</v>
       </c>
       <c r="R11" t="n">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1520,7 +1516,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
